--- a/Compititor's_Price/IKO_Prices/IKO_Prices_09-09-2025.xlsx
+++ b/Compititor's_Price/IKO_Prices/IKO_Prices_09-09-2025.xlsx
@@ -498,17 +498,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£11.53</t>
+          <t>£11.50</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£11.53</t>
+          <t>£11.50</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£11.53</t>
+          <t>£11.50</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -555,17 +555,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£12.95</t>
+          <t>£12.92</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£12.95</t>
+          <t>£12.92</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£12.95</t>
+          <t>£12.92</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -726,17 +726,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£22.05</t>
+          <t>£21.62</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£22.05</t>
+          <t>£21.62</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£22.05</t>
+          <t>£21.62</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -897,17 +897,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£27.72</t>
+          <t>£27.08</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£27.72</t>
+          <t>£27.08</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£27.72</t>
+          <t>£27.08</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£29.77</t>
+          <t>£29.40</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£29.77</t>
+          <t>£29.40</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£29.77</t>
+          <t>£29.40</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1068,17 +1068,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£38.33</t>
+          <t>£38.12</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£38.33</t>
+          <t>£38.12</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>£38.33</t>
+          <t>£38.12</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£46.19</t>
+          <t>£44.10</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£46.19</t>
+          <t>£44.10</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£46.19</t>
+          <t>£44.10</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
